--- a/docs/gowns-ui-labels-zh.xlsx
+++ b/docs/gowns-ui-labels-zh.xlsx
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -250,6 +250,7 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -615,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" style="12" min="1" max="1"/>
@@ -1544,36 +1545,62 @@
       </c>
       <c r="G35" s="17" t="inlineStr">
         <is>
-          <t>Contiene un &lt;br/&gt; tra 'favorites' e 'along'. 'favorites' in ortografia US.</t>
+          <t>'favorites' in ortografia US. (Il &lt;br/&gt; precedente e' stato rimosso: ora riga singola.)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" s="12">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>WISHLIST / FAVOURITE  (page_name V:gowns:favourite:listing page)</t>
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>CLOSET-003</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>Gowns Closet (griglia)</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>Filter by</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>src/components/GridView.tsx → bottone che apre il drawer filtri</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr"/>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>Serif corsivo; grigio, diventa nero con pallino quando un filtro e' attivo.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" s="12">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>WISH-001</t>
+          <t>CLOSET-004</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>Wishlist (Favourite)</t>
+          <t>Gowns Closet (filtro)</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Your Exclusive Selection</t>
+          <t>Refine your selection</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
         <is>
-          <t>src/components/WishlistView.tsx → &lt;h1&gt;</t>
+          <t>src/components/GridView.tsx → intestazione drawer (span) + aria-label del dialog</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr"/>
@@ -1582,27 +1609,31 @@
           <t>Si</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr"/>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>Titolo del pannello filtri.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1" s="12">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>WISH-002</t>
+          <t>CLOSET-005</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>Wishlist (Favourite)</t>
+          <t>Gowns Closet (filtro)</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>No creations selected yet</t>
+          <t>Sizes</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>src/components/WishlistView.tsx → stato vuoto &lt;p&gt;</t>
+          <t>src/components/GridView.tsx → &lt;h3&gt; sezione taglie nel drawer</t>
         </is>
       </c>
       <c r="E38" s="18" t="inlineStr"/>
@@ -1611,27 +1642,31 @@
           <t>Si</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr"/>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>Intestazione sezione (uppercase).</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="29" customHeight="1" s="12">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>WISH-003</t>
+          <t>CLOSET-006</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>Wishlist / Shared</t>
+          <t>Gowns Closet (filtro)</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>{description}</t>
+          <t>{size}</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
         <is>
-          <t>WishlistView.tsx e SharedWishlistView.tsx → &lt;h3&gt; titolo item</t>
+          <t>src/components/GridView.tsx → chip taglia (da product.sizes)</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr"/>
@@ -1640,31 +1675,31 @@
           <t>Si</t>
         </is>
       </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>Dinamico da catalogo.</t>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>⚠ Dinamico dal catalogo (taglie EU). Valori numerici: se la convenzione lo richiede, resi in numeri cinesi. Elenco nel foglio 'Dynamic Content'.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="29" customHeight="1" s="12">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>WISH-004</t>
+          <t>CLOSET-007</t>
         </is>
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>Wishlist / Shared</t>
+          <t>Gowns Closet (filtro)</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>WishlistView.tsx e SharedWishlistView.tsx → riga colore item, forma "Color {colore}"</t>
+          <t>src/components/GridView.tsx → bottone azzera (footer drawer)</t>
         </is>
       </c>
       <c r="E40" s="18" t="inlineStr"/>
@@ -1675,29 +1710,29 @@
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>Testo fisso (MAIUSCOLO) prima del nome colore. Il colore e' dinamico. Incoerente con 'color' minuscolo della PDP (PDP-002).</t>
+          <t>Azzera la selezione taglie nel drawer (uppercase).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" s="12">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>WISH-005</t>
+          <t>CLOSET-008</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>Wishlist / Shared</t>
+          <t>Gowns Closet (filtro)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>{product.sku}</t>
+          <t>Apply</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
         <is>
-          <t>WishlistView.tsx e SharedWishlistView.tsx → codice item</t>
+          <t>src/components/GridView.tsx → bottone applica (footer drawer)</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr"/>
@@ -1708,76 +1743,98 @@
       </c>
       <c r="G41" s="17" t="inlineStr">
         <is>
-          <t>Dinamico (SKU).</t>
+          <t>Applica il filtro taglie (uppercase).</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" s="12">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>SHARED WISHLIST  (page_name V:gowns:favourite:shared page)</t>
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>CLOSET-009</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>Gowns Closet (filtro)</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>No creations match the selected sizes.</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>src/components/GridView.tsx → messaggio stato vuoto (difensivo)</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr"/>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>Mostrato solo se nessuna creazione ha le taglie selezionate.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1" s="12">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>SHARED-001</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>Shared selection</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>Shared selection of creations</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>src/components/SharedWishlistView.tsx → &lt;h1&gt;</t>
-        </is>
-      </c>
-      <c r="E43" s="18" t="inlineStr"/>
-      <c r="F43" s="16" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>WISHLIST / FAVOURITE  (page_name V:gowns:favourite:listing page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" s="12">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>WISH-001</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Wishlist (Favourite)</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>Your Exclusive Selection</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>src/components/WishlistView.tsx → &lt;h1&gt;</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr"/>
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
-        <is>
-          <t>Le righe item riusano il testo fisso 'Color' (WISH-004); titolo/colore/sku degli item sono dinamici (foglio 'Dynamic Content').</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1" s="12">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>COOKIE POLICY  (/cookie-policy/)  -  testo legale verbatim</t>
-        </is>
-      </c>
+      <c r="G44" s="17" t="inlineStr"/>
     </row>
     <row r="45" ht="29" customHeight="1" s="12">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-001</t>
+          <t>WISH-002</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy</t>
+          <t>Wishlist (Favourite)</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>Cookie policy</t>
+          <t>No creations selected yet</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
-          <t>src/app/cookie-policy/page.tsx → &lt;h1&gt; e metadata.description</t>
+          <t>src/components/WishlistView.tsx → stato vuoto &lt;p&gt;</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr"/>
@@ -1786,31 +1843,27 @@
           <t>Si</t>
         </is>
       </c>
-      <c r="G45" s="17" t="inlineStr">
-        <is>
-          <t>Stesso testo per H1 e meta description. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
-        </is>
-      </c>
+      <c r="G45" s="17" t="inlineStr"/>
     </row>
     <row r="46" ht="29" customHeight="1" s="12">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-002</t>
+          <t>WISH-003</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy</t>
+          <t>Wishlist / Shared</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>What is a cookie and what are they used for?</t>
+          <t>{description}</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
+          <t>WishlistView.tsx e SharedWishlistView.tsx → &lt;h3&gt; titolo item</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr"/>
@@ -1821,29 +1874,29 @@
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Dinamico da catalogo.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="29" customHeight="1" s="12">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-003</t>
+          <t>WISH-004</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy</t>
+          <t>Wishlist / Shared</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>A cookie is a small data file which, in the form of a unique anonymous code, is sent to your browser from a web server and then stored on the hard disk of your device (computer, smart-phone and/or tablet). Cookies may allow the correct use of an internet site (so-called technical or necessary cookies), or they may act as checks of the User's preferences in the context of the latter's online navigation in order to propose advertising messages (so-called profiling cookies). Cookies may be stored permanently on the device for a period of variable duration (so-called permanent cookies), or they may be deleted on the closure of the browser or be of limited duration (so-called session cookies). Cookies may be installed by the website you are visiting (so-called first party cookies) or may be installed by other websites (so-called third-party cookies).</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
+          <t>WishlistView.tsx e SharedWishlistView.tsx → riga colore item, forma "Color {colore}"</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr"/>
@@ -1854,29 +1907,29 @@
       </c>
       <c r="G47" s="17" t="inlineStr">
         <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Testo fisso (MAIUSCOLO) prima del nome colore. Il colore e' dinamico. Incoerente con 'color' minuscolo della PDP (PDP-002).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1" s="12">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-004</t>
+          <t>WISH-005</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy</t>
+          <t>Wishlist / Shared</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>The cookies used on this website and the purposes of such use</t>
+          <t>{product.sku}</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
+          <t>WishlistView.tsx e SharedWishlistView.tsx → codice item</t>
         </is>
       </c>
       <c r="E48" s="18" t="inlineStr"/>
@@ -1887,62 +1940,36 @@
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="29" customHeight="1" s="12">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>COOKIE-005</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>Cookie Policy</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>This Website uses the following cookies:</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="inlineStr">
-        <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
-        </is>
-      </c>
-      <c r="E49" s="18" t="inlineStr"/>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="inlineStr">
-        <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Dinamico (SKU).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" s="12">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>SHARED WISHLIST  (page_name V:gowns:favourite:shared page)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" s="12">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-006</t>
+          <t>SHARED-001</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy</t>
+          <t>Shared selection</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>Necessary/Technical cookies</t>
+          <t>Shared selection of creations</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;h3&gt;</t>
+          <t>src/components/SharedWishlistView.tsx → &lt;h1&gt;</t>
         </is>
       </c>
       <c r="E50" s="18" t="inlineStr"/>
@@ -1953,47 +1980,21 @@
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Le righe item riusano il testo fisso 'Color' (WISH-004); titolo/colore/sku degli item sono dinamici (foglio 'Dynamic Content').</t>
         </is>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" s="12">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>COOKIE-007</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>Cookie Policy</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>These cookies allow the Website to function correctly making it possible to view its contents in the related language and market from the User's first visit, then this is the purpose of said necessary technical cookies. They are able to recognize the country from which User is making the connection and ensure that the User is automatically orientated to the version of the Website applicable for his or her country on each visit. These cookies are necessary for the functioning of the Website.</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
-        </is>
-      </c>
-      <c r="E51" s="18" t="inlineStr"/>
-      <c r="F51" s="16" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="G51" s="17" t="inlineStr">
-        <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>COOKIE POLICY  (/cookie-policy/)  -  testo legale verbatim</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" s="12">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-008</t>
+          <t>COOKIE-001</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
@@ -2003,12 +2004,12 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>List of cookies</t>
+          <t>Cookie policy</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;h3&gt;</t>
+          <t>src/app/cookie-policy/page.tsx → &lt;h1&gt; e metadata.description</t>
         </is>
       </c>
       <c r="E52" s="18" t="inlineStr"/>
@@ -2019,14 +2020,14 @@
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Stesso testo per H1 e meta description. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" s="12">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-009</t>
+          <t>COOKIE-002</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -2036,12 +2037,12 @@
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>A cookie is a small amount of data (a text file) that a website, asks the browser to store on the device when visited by a user in order to remember their information, such as their preferred language or login details. These cookies are set by us and called first-party cookies. We also use third-party cookies (cookies from a domain other than the website you are visiting) for advertising and marketing purposes. In particular, we use cookies and other tracking technologies for these purposes:</t>
+          <t>What is a cookie and what are they used for?</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr"/>
@@ -2059,22 +2060,22 @@
     <row r="54" ht="43.5" customHeight="1" s="12">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-011</t>
+          <t>COOKIE-003</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy (tabella)</t>
+          <t>Cookie Policy</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>Cookie Subgroup</t>
+          <t>A cookie is a small data file which, in the form of a unique anonymous code, is sent to your browser from a web server and then stored on the hard disk of your device (computer, smart-phone and/or tablet). Cookies may allow the correct use of an internet site (so-called technical or necessary cookies), or they may act as checks of the User's preferences in the context of the latter's online navigation in order to propose advertising messages (so-called profiling cookies). Cookies may be stored permanently on the device for a period of variable duration (so-called permanent cookies), or they may be deleted on the closure of the browser or be of limited duration (so-called session cookies). Cookies may be installed by the website you are visiting (so-called first party cookies) or may be installed by other websites (so-called third-party cookies).</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;th&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E54" s="18" t="inlineStr"/>
@@ -2092,22 +2093,22 @@
     <row r="55" ht="29" customHeight="1" s="12">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-012</t>
+          <t>COOKIE-004</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy (tabella)</t>
+          <t>Cookie Policy</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Cookies</t>
+          <t>The cookies used on this website and the purposes of such use</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;th&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
         </is>
       </c>
       <c r="E55" s="18" t="inlineStr"/>
@@ -2125,22 +2126,22 @@
     <row r="56" ht="20" customHeight="1" s="12">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-013</t>
+          <t>COOKIE-005</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy (tabella)</t>
+          <t>Cookie Policy</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>This Website uses the following cookies:</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;th&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E56" s="18" t="inlineStr"/>
@@ -2158,22 +2159,22 @@
     <row r="57" ht="43.5" customHeight="1" s="12">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-014</t>
+          <t>COOKIE-006</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy (tabella)</t>
+          <t>Cookie Policy</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Cookies used</t>
+          <t>Necessary/Technical cookies</t>
         </is>
       </c>
       <c r="D57" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;th&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;h3&gt;</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr"/>
@@ -2191,22 +2192,22 @@
     <row r="58" ht="20" customHeight="1" s="12">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-015</t>
+          <t>COOKIE-007</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy (tabella)</t>
+          <t>Cookie Policy</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>Lifespan</t>
+          <t>These cookies allow the Website to function correctly making it possible to view its contents in the related language and market from the User's first visit, then this is the purpose of said necessary technical cookies. They are able to recognize the country from which User is making the connection and ensure that the User is automatically orientated to the version of the Website applicable for his or her country on each visit. These cookies are necessary for the functioning of the Website.</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;th&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E58" s="18" t="inlineStr"/>
@@ -2224,22 +2225,22 @@
     <row r="59" ht="43.5" customHeight="1" s="12">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-016</t>
+          <t>COOKIE-008</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy (tabella)</t>
+          <t>Cookie Policy</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>*.valentino.com</t>
+          <t>List of cookies</t>
         </is>
       </c>
       <c r="D59" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;th scope=row&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;h3&gt;</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr"/>
@@ -2250,29 +2251,29 @@
       </c>
       <c r="G59" s="17" t="inlineStr">
         <is>
-          <t>Dominio, non tradurre. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1" s="12">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-017</t>
+          <t>COOKIE-009</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy (tabella)</t>
+          <t>Cookie Policy</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>Browser Language</t>
+          <t>A cookie is a small amount of data (a text file) that a website, asks the browser to store on the device when visited by a user in order to remember their information, such as their preferred language or login details. These cookies are set by us and called first-party cookies. We also use third-party cookies (cookies from a domain other than the website you are visiting) for advertising and marketing purposes. In particular, we use cookies and other tracking technologies for these purposes:</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;td&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E60" s="18" t="inlineStr"/>
@@ -2290,7 +2291,7 @@
     <row r="61" ht="58" customHeight="1" s="12">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-018</t>
+          <t>COOKIE-011</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2300,12 +2301,12 @@
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>Default language</t>
+          <t>Cookie Subgroup</t>
         </is>
       </c>
       <c r="D61" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;td&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;th&gt;</t>
         </is>
       </c>
       <c r="E61" s="18" t="inlineStr"/>
@@ -2323,7 +2324,7 @@
     <row r="62" ht="32" customHeight="1" s="12">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-019</t>
+          <t>COOKIE-012</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -2333,12 +2334,12 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>First Party</t>
+          <t>Cookies</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;td&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;th&gt;</t>
         </is>
       </c>
       <c r="E62" s="18" t="inlineStr"/>
@@ -2349,14 +2350,14 @@
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>Ripetuto 3 volte in tabella. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1" s="12">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-020</t>
+          <t>COOKIE-014</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -2366,12 +2367,12 @@
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>Session</t>
+          <t>Cookies used</t>
         </is>
       </c>
       <c r="D63" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;td&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;th&gt;</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr"/>
@@ -2382,14 +2383,14 @@
       </c>
       <c r="G63" s="17" t="inlineStr">
         <is>
-          <t>Ripetuto 3 volte in tabella. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="58" customHeight="1" s="12">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-021</t>
+          <t>COOKIE-015</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -2399,12 +2400,12 @@
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>Operating system, browser type and version</t>
+          <t>Lifespan</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;td&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;th&gt;</t>
         </is>
       </c>
       <c r="E64" s="18" t="inlineStr"/>
@@ -2422,7 +2423,7 @@
     <row r="65" ht="20" customHeight="1" s="12">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-022</t>
+          <t>COOKIE-016</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -2432,12 +2433,12 @@
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>VCard download and QR code render</t>
+          <t>*.valentino.com</t>
         </is>
       </c>
       <c r="D65" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;td&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;th scope=row&gt;</t>
         </is>
       </c>
       <c r="E65" s="18" t="inlineStr"/>
@@ -2448,14 +2449,14 @@
       </c>
       <c r="G65" s="17" t="inlineStr">
         <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Dominio, non tradurre. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="58" customHeight="1" s="12">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-023</t>
+          <t>COOKIE-054</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
@@ -2465,12 +2466,12 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>Viewport dimension</t>
+          <t>Local Storage - Wishlist</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;td&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;td&gt; (colonna Cookies)</t>
         </is>
       </c>
       <c r="E66" s="18" t="inlineStr"/>
@@ -2481,14 +2482,14 @@
       </c>
       <c r="G66" s="17" t="inlineStr">
         <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Cella tabella cookie policy. Testo legale verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx); traduzione da far validare dal Legal.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1" s="12">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-024</t>
+          <t>COOKIE-019</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -2498,7 +2499,7 @@
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>Responsiveness app</t>
+          <t>First Party</t>
         </is>
       </c>
       <c r="D67" s="17" t="inlineStr">
@@ -2514,29 +2515,29 @@
       </c>
       <c r="G67" s="17" t="inlineStr">
         <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Ripetuto 3 volte in tabella. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="58" customHeight="1" s="12">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-025</t>
+          <t>COOKIE-055</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>Cookie Policy</t>
+          <t>Cookie Policy (tabella)</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>Analytic Cookies</t>
+          <t>Forever</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;h3&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;td&gt; (colonna Lifespan)</t>
         </is>
       </c>
       <c r="E68" s="18" t="inlineStr"/>
@@ -2547,14 +2548,14 @@
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Cella tabella cookie policy. Testo legale verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx); traduzione da far validare dal Legal.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="130.5" customHeight="1" s="12">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-026</t>
+          <t>COOKIE-025</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -2564,12 +2565,12 @@
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>These cookies are used to create statistical analyses on the manner in which Users navigate the Website, for example the device used, the number of pages visited or the number of clicks on a particular page during navigation. The results of these analyses are processed in an anonymous way and only for statistics purposes. Then statistical aggregated analysis about the use of the Website is the purposes of the processing. We only use cookies which track anonymous IP addresses (with a portion of the code not visible); such cookies are assimilated to technical cookies as they do not allow any users identification and they do not need any consent to be used.</t>
+          <t>Analytic Cookies</t>
         </is>
       </c>
       <c r="D69" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;h3&gt;</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr"/>
@@ -2587,7 +2588,7 @@
     <row r="70" ht="58" customHeight="1" s="12">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-027</t>
+          <t>COOKIE-026</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
@@ -2597,12 +2598,12 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>Data retention</t>
+          <t>These cookies are used to create statistical analyses on the manner in which Users navigate the Website, for example the device used, the number of pages visited or the number of clicks on a particular page during navigation. The results of these analyses are processed in an anonymous way and only for statistics purposes. Then statistical aggregated analysis about the use of the Website is the purposes of the processing. We only use cookies which track anonymous IP addresses (with a portion of the code not visible); such cookies are assimilated to technical cookies as they do not allow any users identification and they do not need any consent to be used.</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E70" s="18" t="inlineStr"/>
@@ -2620,7 +2621,7 @@
     <row r="71" ht="58" customHeight="1" s="12">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-028</t>
+          <t>COOKIE-027</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
@@ -2630,12 +2631,12 @@
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>Please note that the lifespan of each cookie is indicated within the tables above. The data collected by the cookies will be retained by the Data Controller for a maximum of 37 months and then cancelled or anonymized.</t>
+          <t>Data retention</t>
         </is>
       </c>
       <c r="D71" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr"/>
@@ -2653,7 +2654,7 @@
     <row r="72" ht="58" customHeight="1" s="12">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-029</t>
+          <t>COOKIE-028</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
@@ -2663,12 +2664,12 @@
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>Legal basis for the use of cookies</t>
+          <t>Please note that the lifespan of each cookie is indicated within the tables above. The data collected by the cookies will be retained by the Data Controller for a maximum of 37 months and then cancelled or anonymized.</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E72" s="18" t="inlineStr"/>
@@ -2686,7 +2687,7 @@
     <row r="73" ht="58" customHeight="1" s="12">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-030</t>
+          <t>COOKIE-029</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -2696,12 +2697,12 @@
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>Consent is not required for the use of technical cookies (including anonymized analytical cookies); they are thus processed on the basis of the owner's legitimate interest to provide improved navigation and use of the Website.</t>
+          <t>Legal basis for the use of cookies</t>
         </is>
       </c>
       <c r="D73" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr"/>
@@ -2719,7 +2720,7 @@
     <row r="74" ht="58" customHeight="1" s="12">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-031</t>
+          <t>COOKIE-030</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
@@ -2729,12 +2730,12 @@
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>How your personal data are processed</t>
+          <t>Consent is not required for the use of technical cookies (including anonymized analytical cookies); they are thus processed on the basis of the owner's legitimate interest to provide improved navigation and use of the Website.</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E74" s="18" t="inlineStr"/>
@@ -2752,7 +2753,7 @@
     <row r="75" ht="58" customHeight="1" s="12">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-032</t>
+          <t>COOKIE-031</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
@@ -2762,12 +2763,12 @@
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>Your personal data will be processed by automated tools for the time strictly necessary to achieve the purposes for which such data were collected (please see the specific cookie duration on the tables above and the DATA RETENTION section above). Specific security, technical and organizational measures have been adopted to prevent the loss of data, illicit or incorrect use and unauthorized access.</t>
+          <t>How your personal data are processed</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
         </is>
       </c>
       <c r="E75" s="18" t="inlineStr"/>
@@ -2785,7 +2786,7 @@
     <row r="76" ht="58" customHeight="1" s="12">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-033</t>
+          <t>COOKIE-032</t>
         </is>
       </c>
       <c r="B76" s="17" t="inlineStr">
@@ -2795,12 +2796,12 @@
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>Users right to oppose or edit cookies</t>
+          <t>Your personal data will be processed by automated tools for the time strictly necessary to achieve the purposes for which such data were collected (please see the specific cookie duration on the tables above and the DATA RETENTION section above). Specific security, technical and organizational measures have been adopted to prevent the loss of data, illicit or incorrect use and unauthorized access.</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E76" s="18" t="inlineStr"/>
@@ -2818,7 +2819,7 @@
     <row r="77" ht="58" customHeight="1" s="12">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-034</t>
+          <t>COOKIE-033</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
@@ -2828,12 +2829,12 @@
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>You can oppose the storage of cookies on your hard disk by configuring your browser in such a way as to deactivate cookies. We have set out below the procedures available in the main browsers:</t>
+          <t>Users right to oppose or edit cookies</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
         </is>
       </c>
       <c r="E77" s="18" t="inlineStr"/>
@@ -2851,7 +2852,7 @@
     <row r="78" ht="58" customHeight="1" s="12">
       <c r="A78" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-035</t>
+          <t>COOKIE-034</t>
         </is>
       </c>
       <c r="B78" s="17" t="inlineStr">
@@ -2861,12 +2862,12 @@
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>Chrome: (link support.google.com)</t>
+          <t>You can oppose the storage of cookies on your hard disk by configuring your browser in such a way as to deactivate cookies. We have set out below the procedures available in the main browsers:</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;li&gt; ; href https://support.google.com/chrome/answer/95647?hl=it</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E78" s="18" t="inlineStr"/>
@@ -2877,14 +2878,14 @@
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>Etichetta 'Chrome' + URL. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="58" customHeight="1" s="12">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-036</t>
+          <t>COOKIE-035</t>
         </is>
       </c>
       <c r="B79" s="17" t="inlineStr">
@@ -2894,12 +2895,12 @@
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>Firefox: (link support.mozilla.org)</t>
+          <t>Chrome: (link support.google.com)</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;li&gt; ; href https://support.mozilla.org/it/kb/Gestione%20dei%20cookie</t>
+          <t>cookie-policy/page.tsx → &lt;li&gt; ; href https://support.google.com/chrome/answer/95647?hl=it</t>
         </is>
       </c>
       <c r="E79" s="18" t="inlineStr"/>
@@ -2910,14 +2911,14 @@
       </c>
       <c r="G79" s="17" t="inlineStr">
         <is>
-          <t>Etichetta 'Firefox' + URL. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Etichetta 'Chrome' + URL. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="58" customHeight="1" s="12">
       <c r="A80" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-037</t>
+          <t>COOKIE-036</t>
         </is>
       </c>
       <c r="B80" s="17" t="inlineStr">
@@ -2927,12 +2928,12 @@
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>Safari: (link support.apple.com)</t>
+          <t>Firefox: (link support.mozilla.org)</t>
         </is>
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;li&gt; ; href http://support.apple.com/kb/HT1677?viewlocale=it_IT</t>
+          <t>cookie-policy/page.tsx → &lt;li&gt; ; href https://support.mozilla.org/it/kb/Gestione%20dei%20cookie</t>
         </is>
       </c>
       <c r="E80" s="18" t="inlineStr"/>
@@ -2943,14 +2944,14 @@
       </c>
       <c r="G80" s="17" t="inlineStr">
         <is>
-          <t>Etichetta 'Safari' + URL. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Etichetta 'Firefox' + URL. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="58" customHeight="1" s="12">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-038</t>
+          <t>COOKIE-037</t>
         </is>
       </c>
       <c r="B81" s="17" t="inlineStr">
@@ -2960,12 +2961,12 @@
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>It is possible, however, that after completing the above operation a number of the web page functions may not work properly.</t>
+          <t>Safari: (link support.apple.com)</t>
         </is>
       </c>
       <c r="D81" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;li&gt; ; href http://support.apple.com/kb/HT1677?viewlocale=it_IT</t>
         </is>
       </c>
       <c r="E81" s="18" t="inlineStr"/>
@@ -2976,14 +2977,14 @@
       </c>
       <c r="G81" s="17" t="inlineStr">
         <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Etichetta 'Safari' + URL. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="58" customHeight="1" s="12">
       <c r="A82" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-039</t>
+          <t>COOKIE-038</t>
         </is>
       </c>
       <c r="B82" s="17" t="inlineStr">
@@ -2993,12 +2994,12 @@
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>Data controller</t>
+          <t>It is possible, however, that after completing the above operation a number of the web page functions may not work properly.</t>
         </is>
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E82" s="18" t="inlineStr"/>
@@ -3016,7 +3017,7 @@
     <row r="83" ht="58" customHeight="1" s="12">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-040</t>
+          <t>COOKIE-039</t>
         </is>
       </c>
       <c r="B83" s="17" t="inlineStr">
@@ -3026,12 +3027,12 @@
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>The data controller of data collected by cookies is Valentino S.p.A. with registered office in Via Turati 16/18, 20121, Milano (MI), Italia. Valentino S.p.A. has appointed a data protection officer, who can be contacted at the following e-mail address privacy@valentino.com. For any information regarding the processing of your personal data, to complain and to exercise the rights set out below, you can also contact the data controller writing to Valentino, via Turati 16/18, 20121 Milano (at the attention of the Legal Department, which is appointed to receive and manage such requests, also involving the relevant departments, as per the internal Valentino procedures).</t>
+          <t>Data controller</t>
         </is>
       </c>
       <c r="D83" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
         </is>
       </c>
       <c r="E83" s="18" t="inlineStr"/>
@@ -3042,14 +3043,14 @@
       </c>
       <c r="G83" s="17" t="inlineStr">
         <is>
-          <t>Contiene indirizzo ed email. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="84" ht="58" customHeight="1" s="12">
       <c r="A84" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-041</t>
+          <t>COOKIE-040</t>
         </is>
       </c>
       <c r="B84" s="17" t="inlineStr">
@@ -3059,12 +3060,12 @@
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>Who will obtain knowledge of the data, their transfer and disclosure</t>
+          <t>The data controller of data collected by cookies is Valentino S.p.A. with registered office in Via Turati 16/18, 20121, Milano (MI), Italia. Valentino S.p.A. has appointed a data protection officer, who can be contacted at the following e-mail address privacy@valentino.com. For any information regarding the processing of your personal data, to complain and to exercise the rights set out below, you can also contact the data controller writing to Valentino, via Turati 16/18, 20121 Milano (at the attention of the Legal Department, which is appointed to receive and manage such requests, also involving the relevant departments, as per the internal Valentino procedures).</t>
         </is>
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E84" s="18" t="inlineStr"/>
@@ -3075,14 +3076,14 @@
       </c>
       <c r="G84" s="17" t="inlineStr">
         <is>
-          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
+          <t>Contiene indirizzo ed email. Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="58" customHeight="1" s="12">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-042</t>
+          <t>COOKIE-041</t>
         </is>
       </c>
       <c r="B85" s="17" t="inlineStr">
@@ -3092,12 +3093,12 @@
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>The data acquired by cookies will and may come to the knowledge of the following:</t>
+          <t>Who will obtain knowledge of the data, their transfer and disclosure</t>
         </is>
       </c>
       <c r="D85" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr"/>
@@ -3115,7 +3116,7 @@
     <row r="86" ht="174" customHeight="1" s="12">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-043</t>
+          <t>COOKIE-042</t>
         </is>
       </c>
       <c r="B86" s="17" t="inlineStr">
@@ -3125,12 +3126,12 @@
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>Employees and collaborators of the controller, acting in the capacity of person authorized to effect processing; and,</t>
+          <t>The data acquired by cookies will and may come to the knowledge of the following:</t>
         </is>
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;li&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E86" s="18" t="inlineStr"/>
@@ -3148,7 +3149,7 @@
     <row r="87" ht="58" customHeight="1" s="12">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-044</t>
+          <t>COOKIE-043</t>
         </is>
       </c>
       <c r="B87" s="17" t="inlineStr">
@@ -3158,7 +3159,7 @@
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>Suppliers of technical and organizational services acting in the capacity of processors.</t>
+          <t>Employees and collaborators of the controller, acting in the capacity of person authorized to effect processing; and,</t>
         </is>
       </c>
       <c r="D87" s="17" t="inlineStr">
@@ -3181,7 +3182,7 @@
     <row r="88" ht="58" customHeight="1" s="12">
       <c r="A88" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-045</t>
+          <t>COOKIE-044</t>
         </is>
       </c>
       <c r="B88" s="17" t="inlineStr">
@@ -3191,12 +3192,12 @@
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>We may transfer the data acquired by the use of cookies abroad including to countries outside the EU, with the guarantee nonetheless, of appropriate protections and defenses. To obtain information on the exact location of the data you are invited to write to the controller at privacy@valentino.com.</t>
+          <t>Suppliers of technical and organizational services acting in the capacity of processors.</t>
         </is>
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;li&gt;</t>
         </is>
       </c>
       <c r="E88" s="18" t="inlineStr"/>
@@ -3214,7 +3215,7 @@
     <row r="89" ht="58" customHeight="1" s="12">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-046</t>
+          <t>COOKIE-045</t>
         </is>
       </c>
       <c r="B89" s="17" t="inlineStr">
@@ -3224,7 +3225,7 @@
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>The data will not be disclosed generally in any way.</t>
+          <t>We may transfer the data acquired by the use of cookies abroad including to countries outside the EU, with the guarantee nonetheless, of appropriate protections and defenses. To obtain information on the exact location of the data you are invited to write to the controller at privacy@valentino.com.</t>
         </is>
       </c>
       <c r="D89" s="17" t="inlineStr">
@@ -3247,7 +3248,7 @@
     <row r="90" ht="58" customHeight="1" s="12">
       <c r="A90" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-047</t>
+          <t>COOKIE-046</t>
         </is>
       </c>
       <c r="B90" s="17" t="inlineStr">
@@ -3257,12 +3258,12 @@
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>Users rights</t>
+          <t>The data will not be disclosed generally in any way.</t>
         </is>
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E90" s="18" t="inlineStr"/>
@@ -3280,7 +3281,7 @@
     <row r="91" ht="58" customHeight="1" s="12">
       <c r="A91" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-048</t>
+          <t>COOKIE-047</t>
         </is>
       </c>
       <c r="B91" s="17" t="inlineStr">
@@ -3290,12 +3291,12 @@
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>The user always has the right to obtain from VALENTINO confirmation of whether or not personal data concerning him/her exists, even if it is not yet recorded, and to have it communicated to him/her in an intelligible form. A user also has the right to obtain information about the source of personal data; the purposes and methods of processing it, the logic applied in the event of processing that is performed with the aid of electronic instruments; the identification details of the controller and data processors; and indication of the persons or categories of persons whose personal data may be communicated. A user also has the right to request an update, correction or, when s/he has an interest in doing so, an inclusion of personal data, deletion, conversion to an anonymous form or the blocking of personal data, that has been processed in violation of the law, including data which it is not necessary to keep in relation to the purposes for which it was collected or subsequently processed; a statement that the above operations were disclosed, including in terms of their content, to those parties to whom the data was communicated, except in the case in which such performance proves impossible or entails the use of methods that are clearly disproportionate to the right protected. The user can also ask for the portability of his/her data. Moreover, the user has the right to ask restriction of processing of his/her personal data.</t>
+          <t>Users rights</t>
         </is>
       </c>
       <c r="D91" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
+          <t>cookie-policy/page.tsx → &lt;h2&gt;</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr"/>
@@ -3313,7 +3314,7 @@
     <row r="92" ht="101.5" customHeight="1" s="12">
       <c r="A92" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-049</t>
+          <t>COOKIE-048</t>
         </is>
       </c>
       <c r="B92" s="17" t="inlineStr">
@@ -3323,7 +3324,7 @@
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>A user nevertheless has the right to object, in part or in full, for legitimate reasons, the processing of personal data concerning him/her, even if it is pertinent to the scope of the collection.</t>
+          <t>The user always has the right to obtain from VALENTINO confirmation of whether or not personal data concerning him/her exists, even if it is not yet recorded, and to have it communicated to him/her in an intelligible form. A user also has the right to obtain information about the source of personal data; the purposes and methods of processing it, the logic applied in the event of processing that is performed with the aid of electronic instruments; the identification details of the controller and data processors; and indication of the persons or categories of persons whose personal data may be communicated. A user also has the right to request an update, correction or, when s/he has an interest in doing so, an inclusion of personal data, deletion, conversion to an anonymous form or the blocking of personal data, that has been processed in violation of the law, including data which it is not necessary to keep in relation to the purposes for which it was collected or subsequently processed; a statement that the above operations were disclosed, including in terms of their content, to those parties to whom the data was communicated, except in the case in which such performance proves impossible or entails the use of methods that are clearly disproportionate to the right protected. The user can also ask for the portability of his/her data. Moreover, the user has the right to ask restriction of processing of his/her personal data.</t>
         </is>
       </c>
       <c r="D92" s="17" t="inlineStr">
@@ -3346,7 +3347,7 @@
     <row r="93" ht="58" customHeight="1" s="12">
       <c r="A93" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-050</t>
+          <t>COOKIE-049</t>
         </is>
       </c>
       <c r="B93" s="17" t="inlineStr">
@@ -3356,7 +3357,7 @@
       </c>
       <c r="C93" s="17" t="inlineStr">
         <is>
-          <t>You can exercise the above rights and ask information and further questions about the processing of your Personal Data by contacting VALENTINO and the Data Protection Officer writing to privacy@valentino.com (please note that the delivery of an email request entails the subsequent acquisition of the sender's address, necessary to respond to requests and keep track of them, as well as any other personal data included in the electronic communication, for legal purposes). You can also write by mail at VALENTINO, via Turati 16/18, 20121, Milano (Italy), at the attention of the Legal Department.</t>
+          <t>A user nevertheless has the right to object, in part or in full, for legitimate reasons, the processing of personal data concerning him/her, even if it is pertinent to the scope of the collection.</t>
         </is>
       </c>
       <c r="D93" s="17" t="inlineStr">
@@ -3379,7 +3380,7 @@
     <row r="94" ht="58" customHeight="1" s="12">
       <c r="A94" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-051</t>
+          <t>COOKIE-050</t>
         </is>
       </c>
       <c r="B94" s="17" t="inlineStr">
@@ -3389,7 +3390,7 @@
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>Please finally note that you have the right to lodge a complaint with the Italian Data Protection Authority (Garante per la Protezione dei Dati Personali), based in Piazza Venezia, 11, 00187 Rome (www.garanteprivacy.it), or with another data protection supervisory authority in the Country in which you reside.</t>
+          <t>You can exercise the above rights and ask information and further questions about the processing of your Personal Data by contacting VALENTINO and the Data Protection Officer writing to privacy@valentino.com (please note that the delivery of an email request entails the subsequent acquisition of the sender's address, necessary to respond to requests and keep track of them, as well as any other personal data included in the electronic communication, for legal purposes). You can also write by mail at VALENTINO, via Turati 16/18, 20121, Milano (Italy), at the attention of the Legal Department.</t>
         </is>
       </c>
       <c r="D94" s="17" t="inlineStr">
@@ -3412,7 +3413,7 @@
     <row r="95" ht="58" customHeight="1" s="12">
       <c r="A95" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-052</t>
+          <t>COOKIE-051</t>
         </is>
       </c>
       <c r="B95" s="17" t="inlineStr">
@@ -3422,12 +3423,12 @@
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>privacy@valentino.com</t>
+          <t>Please finally note that you have the right to lodge a complaint with the Italian Data Protection Authority (Garante per la Protezione dei Dati Personali), based in Piazza Venezia, 11, 00187 Rome (www.garanteprivacy.it), or with another data protection supervisory authority in the Country in which you reside.</t>
         </is>
       </c>
       <c r="D95" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → link mailto (4 occorrenze)</t>
+          <t>cookie-policy/page.tsx → &lt;p&gt;</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr"/>
@@ -3438,14 +3439,14 @@
       </c>
       <c r="G95" s="17" t="inlineStr">
         <is>
-          <t>Email visibile, non tradurre.</t>
+          <t>Testo legale, verbatim dal documento approvato (Cookie Policy/Gowns Cookie Policy.docx). Traduzione da far validare dal Legal; non riscrivere/riassumere.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="58" customHeight="1" s="12">
       <c r="A96" s="16" t="inlineStr">
         <is>
-          <t>COOKIE-053</t>
+          <t>COOKIE-052</t>
         </is>
       </c>
       <c r="B96" s="17" t="inlineStr">
@@ -3455,12 +3456,12 @@
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>www.garanteprivacy.it</t>
+          <t>privacy@valentino.com</t>
         </is>
       </c>
       <c r="D96" s="17" t="inlineStr">
         <is>
-          <t>cookie-policy/page.tsx → testo link ; href http://www.garanteprivacy.it/</t>
+          <t>cookie-policy/page.tsx → link mailto (4 occorrenze)</t>
         </is>
       </c>
       <c r="E96" s="18" t="inlineStr"/>
@@ -3471,11 +3472,43 @@
       </c>
       <c r="G96" s="17" t="inlineStr">
         <is>
+          <t>Email visibile, non tradurre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="58" customHeight="1" s="12">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>COOKIE-053</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>Cookie Policy</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>www.garanteprivacy.it</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="inlineStr">
+        <is>
+          <t>cookie-policy/page.tsx → testo link ; href http://www.garanteprivacy.it/</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="inlineStr"/>
+      <c r="F97" s="16" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G97" s="17" t="inlineStr">
+        <is>
           <t>URL visibile, non tradurre.</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="58" customHeight="1" s="12"/>
     <row r="98" ht="58" customHeight="1" s="12"/>
     <row r="99" ht="58" customHeight="1" s="12"/>
     <row r="100" ht="174" customHeight="1" s="12"/>
@@ -3501,16 +3534,16 @@
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <mergeCells count="10">
-    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A49:G49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3522,7 +3555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="12" min="1" max="1"/>
@@ -3766,12 +3799,12 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>Alt di /logo-valentino.svg. Usato in: page.tsx (header login), MenuScreen.tsx, Header.tsx, SharedWishlistView.tsx, cookie-policy/page.tsx</t>
+          <t>src/app/page.tsx → alt di /logo-valentino.svg (solo header login)</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>Alt immagine logo</t>
+          <t>Alt immagine logo (non reso a schermo)</t>
         </is>
       </c>
     </row>
@@ -4123,6 +4156,60 @@
       <c r="E22" s="17" t="inlineStr">
         <is>
           <t>Caption sr-only (solo screen reader)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>CLOSET-010</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Gowns Closet (filtro)</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>src/components/GridView.tsx → bottone chiusura drawer, aria-label</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>aria-label (il bottone mostra il simbolo ×, non testo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>GLOB-003</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Globale (logo)</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Valentino Garavani</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>alt di /logo-valentino-garavani.png in Header.tsx, MenuScreen.tsx, SharedWishlistView.tsx, cookie-policy/page.tsx</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>Alt immagine logo (non reso a schermo)</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" style="12" min="1" max="1"/>
@@ -8142,11 +8229,271 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="20" t="inlineStr">
+        <is>
+          <t>TAGLIE / CHIP FILTRO (distinct: 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="17" t="inlineStr">
+        <is>
+          <t>SIZE-001</t>
+        </is>
+      </c>
+      <c r="B146" s="17" t="inlineStr">
+        <is>
+          <t>taglia</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D146" s="17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E146" s="18" t="inlineStr"/>
+      <c r="F146" s="17" t="inlineStr">
+        <is>
+          <t>Chip del filtro taglie (GridView.tsx). Valore numerico dal catalogo (product.sizes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="17" t="inlineStr">
+        <is>
+          <t>SIZE-002</t>
+        </is>
+      </c>
+      <c r="B147" s="17" t="inlineStr">
+        <is>
+          <t>taglia</t>
+        </is>
+      </c>
+      <c r="C147" s="17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D147" s="17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E147" s="18" t="inlineStr"/>
+      <c r="F147" s="17" t="inlineStr">
+        <is>
+          <t>Chip del filtro taglie (GridView.tsx). Valore numerico dal catalogo (product.sizes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="17" t="inlineStr">
+        <is>
+          <t>SIZE-003</t>
+        </is>
+      </c>
+      <c r="B148" s="17" t="inlineStr">
+        <is>
+          <t>taglia</t>
+        </is>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D148" s="17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E148" s="18" t="inlineStr"/>
+      <c r="F148" s="17" t="inlineStr">
+        <is>
+          <t>Chip del filtro taglie (GridView.tsx). Valore numerico dal catalogo (product.sizes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="17" t="inlineStr">
+        <is>
+          <t>SIZE-004</t>
+        </is>
+      </c>
+      <c r="B149" s="17" t="inlineStr">
+        <is>
+          <t>taglia</t>
+        </is>
+      </c>
+      <c r="C149" s="17" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D149" s="17" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E149" s="18" t="inlineStr"/>
+      <c r="F149" s="17" t="inlineStr">
+        <is>
+          <t>Chip del filtro taglie (GridView.tsx). Valore numerico dal catalogo (product.sizes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="17" t="inlineStr">
+        <is>
+          <t>SIZE-005</t>
+        </is>
+      </c>
+      <c r="B150" s="17" t="inlineStr">
+        <is>
+          <t>taglia</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D150" s="17" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E150" s="18" t="inlineStr"/>
+      <c r="F150" s="17" t="inlineStr">
+        <is>
+          <t>Chip del filtro taglie (GridView.tsx). Valore numerico dal catalogo (product.sizes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="17" t="inlineStr">
+        <is>
+          <t>SIZE-006</t>
+        </is>
+      </c>
+      <c r="B151" s="17" t="inlineStr">
+        <is>
+          <t>taglia</t>
+        </is>
+      </c>
+      <c r="C151" s="17" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D151" s="17" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E151" s="18" t="inlineStr"/>
+      <c r="F151" s="17" t="inlineStr">
+        <is>
+          <t>Chip del filtro taglie (GridView.tsx). Valore numerico dal catalogo (product.sizes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="17" t="inlineStr">
+        <is>
+          <t>SIZE-007</t>
+        </is>
+      </c>
+      <c r="B152" s="17" t="inlineStr">
+        <is>
+          <t>taglia</t>
+        </is>
+      </c>
+      <c r="C152" s="17" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D152" s="17" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E152" s="18" t="inlineStr"/>
+      <c r="F152" s="17" t="inlineStr">
+        <is>
+          <t>Chip del filtro taglie (GridView.tsx). Valore numerico dal catalogo (product.sizes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="17" t="inlineStr">
+        <is>
+          <t>SIZE-008</t>
+        </is>
+      </c>
+      <c r="B153" s="17" t="inlineStr">
+        <is>
+          <t>taglia</t>
+        </is>
+      </c>
+      <c r="C153" s="17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D153" s="17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E153" s="18" t="inlineStr"/>
+      <c r="F153" s="17" t="inlineStr">
+        <is>
+          <t>Chip del filtro taglie (GridView.tsx). Valore numerico dal catalogo (product.sizes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="17" t="inlineStr">
+        <is>
+          <t>SIZE-009</t>
+        </is>
+      </c>
+      <c r="B154" s="17" t="inlineStr">
+        <is>
+          <t>taglia</t>
+        </is>
+      </c>
+      <c r="C154" s="17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D154" s="17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E154" s="18" t="inlineStr"/>
+      <c r="F154" s="17" t="inlineStr">
+        <is>
+          <t>Chip del filtro taglie (GridView.tsx). Valore numerico dal catalogo (product.sizes).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A145:F145"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
